--- a/gte/nodes/LPC/compressor_stage_1_blade_stator_coordinates_foil.xlsx
+++ b/gte/nodes/LPC/compressor_stage_1_blade_stator_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.00088058562931243487</v>
       </c>
       <c r="B2">
-        <v>0.0004832873769087638</v>
+        <v>0.0004181240403396436</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0017611712586248697</v>
       </c>
       <c r="B3">
-        <v>0.00079245844315155734</v>
+        <v>0.00070263870896168884</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0026417568879373052</v>
       </c>
       <c r="B4">
-        <v>0.0010671095306338196</v>
+        <v>0.00095826914685080255</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0035223425172497395</v>
       </c>
       <c r="B5">
-        <v>0.0013150937597649801</v>
+        <v>0.001190931186031927</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0044029281465621743</v>
       </c>
       <c r="B6">
-        <v>0.0015396651913460776</v>
+        <v>0.0014030896346490357</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.00528351377587461</v>
       </c>
       <c r="B7">
-        <v>0.001742712714279027</v>
+        <v>0.0015961832655614376</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.0061640994051870446</v>
       </c>
       <c r="B8">
-        <v>0.0019253776812140808</v>
+        <v>0.0017710891481624938</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.007044685034499479</v>
       </c>
       <c r="B9">
-        <v>0.0020893903183097063</v>
+        <v>0.001929123733774843</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.0079252706638119133</v>
       </c>
       <c r="B10">
-        <v>0.00223660880480591</v>
+        <v>0.0020716983564261289</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.0088058562931243485</v>
       </c>
       <c r="B11">
-        <v>0.0023688142587606539</v>
+        <v>0.0022001644990347364</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.0096864419224367837</v>
       </c>
       <c r="B12">
-        <v>0.0024869814753035995</v>
+        <v>0.0023152679040567554</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.010567027551749221</v>
       </c>
       <c r="B13">
-        <v>0.0025889370190332523</v>
+        <v>0.0024153912032083579</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.011447613181061654</v>
       </c>
       <c r="B14">
-        <v>0.0026733966919689233</v>
+        <v>0.0024995829692292062</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.012328198810374089</v>
       </c>
       <c r="B15">
-        <v>0.00274578147634429</v>
+        <v>0.0025719186496928432</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.013208784439686523</v>
       </c>
       <c r="B16">
-        <v>0.0028110633246442016</v>
+        <v>0.00263613607903188</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.014089370068998958</v>
       </c>
       <c r="B17">
-        <v>0.0028657128901438209</v>
+        <v>0.0026895957642813339</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.014969955698311395</v>
       </c>
       <c r="B18">
-        <v>0.0029051601268274452</v>
+        <v>0.0027288766143572915</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.015850541327623827</v>
       </c>
       <c r="B19">
-        <v>0.0029291734907255979</v>
+        <v>0.0027538084730977272</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.016731126956936262</v>
       </c>
       <c r="B20">
-        <v>0.0029386060633803577</v>
+        <v>0.0027650339180710854</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.017611712586248697</v>
       </c>
       <c r="B21">
-        <v>0.0029343109263338029</v>
+        <v>0.0027631955268458104</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.018492298215561132</v>
       </c>
       <c r="B22">
-        <v>0.0029169877125839938</v>
+        <v>0.0027488198863530873</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.019372883844873567</v>
       </c>
       <c r="B23">
-        <v>0.0028867222609529138</v>
+        <v>0.0027219696209750542</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.020253469474186003</v>
       </c>
       <c r="B24">
-        <v>0.00284344696171853</v>
+        <v>0.0026825913644565906</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.021134055103498441</v>
       </c>
       <c r="B25">
-        <v>0.0027870942051588061</v>
+        <v>0.0026306317505425726</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.02201464073281087</v>
       </c>
       <c r="B26">
-        <v>0.0027175682286488668</v>
+        <v>0.0025660154131683156</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.022895226362123308</v>
       </c>
       <c r="B27">
-        <v>0.002634660657952463</v>
+        <v>0.0024885789870308689</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.023775811991435743</v>
       </c>
       <c r="B28">
-        <v>0.0025381349659305053</v>
+        <v>0.002398137107017717</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.024656397620748179</v>
       </c>
       <c r="B29">
-        <v>0.002427754625443904</v>
+        <v>0.0022945044080163461</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.025536983250060614</v>
       </c>
       <c r="B30">
-        <v>0.0023033911529639975</v>
+        <v>0.0021775756209379397</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.026417568879373046</v>
       </c>
       <c r="B31">
-        <v>0.0021653482394038428</v>
+        <v>0.002047565860788479</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.027298154508685481</v>
       </c>
       <c r="B32">
-        <v>0.0020140376192869232</v>
+        <v>0.0019047703385976418</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.028178740137997916</v>
       </c>
       <c r="B33">
-        <v>0.0018498710271367238</v>
+        <v>0.0017494842653951064</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.029059325767310351</v>
       </c>
       <c r="B34">
-        <v>0.0016730755535509191</v>
+        <v>0.00158186330527637</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.02993991139662279</v>
       </c>
       <c r="B35">
-        <v>0.0014831397134239383</v>
+        <v>0.0014015049346001989</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.030820497025935222</v>
       </c>
       <c r="B36">
-        <v>0.0012793673777244025</v>
+        <v>0.0012078670827911778</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.031701082655247653</v>
       </c>
       <c r="B37">
-        <v>0.0010610624174209288</v>
+        <v>0.0010004076792738885</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.032581668284560092</v>
       </c>
       <c r="B38">
-        <v>0.00082708192614557431</v>
+        <v>0.00077824851071332639</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.033462253913872524</v>
       </c>
       <c r="B39">
-        <v>0.00057449588818414229</v>
+        <v>0.00053916679273612739</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.034342839543184962</v>
       </c>
       <c r="B40">
-        <v>0.00029992751048587294</v>
+        <v>0.0002806035982093386</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.034342839543184962</v>
       </c>
       <c r="B43">
-        <v>0.0001453362122735988</v>
+        <v>0.00016466012455013311</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.033462253913872524</v>
       </c>
       <c r="B44">
-        <v>0.00029186312460002367</v>
+        <v>0.00032719222004803851</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.032581668284560092</v>
       </c>
       <c r="B45">
-        <v>0.00043641460268758982</v>
+        <v>0.00048524801811983785</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.031701082655247653</v>
       </c>
       <c r="B46">
-        <v>0.00057582451224460487</v>
+        <v>0.00063647925039164537</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.030820497025935222</v>
       </c>
       <c r="B47">
-        <v>0.00070736501825860291</v>
+        <v>0.00077886531319182773</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.02993991139662279</v>
       </c>
       <c r="B48">
-        <v>0.000830061482834022</v>
+        <v>0.00091169626165776136</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.029059325767310351</v>
       </c>
       <c r="B49">
-        <v>0.00094337756735452742</v>
+        <v>0.0010345898156290763</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.028178740137997916</v>
       </c>
       <c r="B50">
-        <v>0.0010467769332037833</v>
+        <v>0.0011471636949454008</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.027298154508685481</v>
       </c>
       <c r="B51">
-        <v>0.0011398993737726704</v>
+        <v>0.0012491666544619518</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.026417568879373046</v>
       </c>
       <c r="B52">
-        <v>0.0012230892104809345</v>
+        <v>0.001340871589096298</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.025536983250060614</v>
       </c>
       <c r="B53">
-        <v>0.0012968668967555377</v>
+        <v>0.0014226824287815953</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.024656397620748179</v>
       </c>
       <c r="B54">
-        <v>0.0013617528860234429</v>
+        <v>0.0014950031034510005</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.023775811991435743</v>
       </c>
       <c r="B55">
-        <v>0.0014181520946281994</v>
+        <v>0.0015581499535409877</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.022895226362123308</v>
       </c>
       <c r="B56">
-        <v>0.0014660072905797084</v>
+        <v>0.0016120889615013031</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.02201464073281087</v>
       </c>
       <c r="B57">
-        <v>0.001505145704804459</v>
+        <v>0.0016566985202850098</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.021134055103498441</v>
       </c>
       <c r="B58">
-        <v>0.0015353945682289392</v>
+        <v>0.0016918570228451723</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.020253469474186003</v>
       </c>
       <c r="B59">
-        <v>0.001556602183623012</v>
+        <v>0.0017174577808849517</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.019372883844873567</v>
       </c>
       <c r="B60">
-        <v>0.0015687011411300357</v>
+        <v>0.0017334537811078956</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.018492298215561132</v>
       </c>
       <c r="B61">
-        <v>0.0015716451027367423</v>
+        <v>0.0017398129289676488</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.017611712586248697</v>
       </c>
       <c r="B62">
-        <v>0.0015653877304298643</v>
+        <v>0.0017365031299178566</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.016731126956936262</v>
       </c>
       <c r="B63">
-        <v>0.0015500289009061769</v>
+        <v>0.0017236010462154494</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.015850541327623827</v>
       </c>
       <c r="B64">
-        <v>0.0015262533497026295</v>
+        <v>0.0017016183673305007</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.014969955698311395</v>
       </c>
       <c r="B65">
-        <v>0.0014948920270662143</v>
+        <v>0.0016711755395363685</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.014089370068998958</v>
       </c>
       <c r="B66">
-        <v>0.0014567758832439248</v>
+        <v>0.0016328930091064119</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.013208784439686523</v>
       </c>
       <c r="B67">
-        <v>0.0014116453597456306</v>
+        <v>0.001586572605357952</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.012328198810374089</v>
       </c>
       <c r="B68">
-        <v>0.0013548788631327134</v>
+        <v>0.0015287416897841603</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.011447613181061654</v>
       </c>
       <c r="B69">
-        <v>0.0012828869100511876</v>
+        <v>0.0014567006327909045</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.010567027551749221</v>
       </c>
       <c r="B70">
-        <v>0.0012005704924340952</v>
+        <v>0.0013741163082589898</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.0096864419224367837</v>
       </c>
       <c r="B71">
-        <v>0.0011132729053288475</v>
+        <v>0.0012849864765756914</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.0088058562931243485</v>
       </c>
       <c r="B72">
-        <v>0.0010196161809533139</v>
+        <v>0.0011882659406792313</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.0079252706638119133</v>
       </c>
       <c r="B73">
-        <v>0.00091732521776766271</v>
+        <v>0.0010822356661474434</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.007044685034499479</v>
       </c>
       <c r="B74">
-        <v>0.000807257642030801</v>
+        <v>0.000967524226565664</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.0061640994051870446</v>
       </c>
       <c r="B75">
-        <v>0.00069106941680138311</v>
+        <v>0.00084535794985297029</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.00528351377587461</v>
       </c>
       <c r="B76">
-        <v>0.00057047712453831348</v>
+        <v>0.00071700657325590267</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0044029281465621743</v>
       </c>
       <c r="B77">
-        <v>0.00044706073776974243</v>
+        <v>0.00058363629446678441</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0035223425172497395</v>
       </c>
       <c r="B78">
-        <v>0.00032179316990055371</v>
+        <v>0.000445955743633607</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0026417568879373052</v>
       </c>
       <c r="B79">
-        <v>0.00019638646036968389</v>
+        <v>0.00030522684415270083</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0017611712586248697</v>
       </c>
       <c r="B80">
-        <v>7.3900569632610511E-05</v>
+        <v>0.00016372030382247891</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.00088058562931243487</v>
       </c>
       <c r="B81">
-        <v>-3.8019315644197658E-05</v>
+        <v>2.7144020924922554E-05</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.00097482695731704306</v>
       </c>
       <c r="B2">
-        <v>0.00068698261582852591</v>
+        <v>0.0006148454209870648</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0019496539146340861</v>
       </c>
       <c r="B3">
-        <v>0.0010910642819922348</v>
+        <v>0.00099163193234589643</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0029244808719511295</v>
       </c>
       <c r="B4">
-        <v>0.001443999713919706</v>
+        <v>0.0013235111019953194</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0038993078292681722</v>
       </c>
       <c r="B5">
-        <v>0.0017587830842117954</v>
+        <v>0.0016213324832300925</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.004874134786585215</v>
       </c>
       <c r="B6">
-        <v>0.0020407746539717283</v>
+        <v>0.001889582617732376</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.005848961743902259</v>
       </c>
       <c r="B7">
-        <v>0.0022930715067042656</v>
+        <v>0.00213086030100671</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0068237887012193013</v>
       </c>
       <c r="B8">
-        <v>0.0025175312490361965</v>
+        <v>0.0023467305725125226</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0077986156585363444</v>
       </c>
       <c r="B9">
-        <v>0.0027169933053738577</v>
+        <v>0.0025395747991421563</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0087734426158533867</v>
       </c>
       <c r="B10">
-        <v>0.0028945114717408419</v>
+        <v>0.00271195210979739</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.00974826957317043</v>
       </c>
       <c r="B11">
-        <v>0.00305301521285021</v>
+        <v>0.00286631635398485</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.010723096530487473</v>
       </c>
       <c r="B12">
-        <v>0.003194096838529204</v>
+        <v>0.0030040062753669324</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.011697923487804518</v>
       </c>
       <c r="B13">
-        <v>0.0033141243703723117</v>
+        <v>0.0031220054736242689</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.012672750445121559</v>
       </c>
       <c r="B14">
-        <v>0.0034109442005161848</v>
+        <v>0.0032185287251346429</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.013647577402438603</v>
       </c>
       <c r="B15">
-        <v>0.0034935404914988762</v>
+        <v>0.0033010706570461993</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.014622404359755644</v>
       </c>
       <c r="B16">
-        <v>0.0035701532871881044</v>
+        <v>0.0033765051183833779</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.015597231317072689</v>
       </c>
       <c r="B17">
-        <v>0.0036349083863688411</v>
+        <v>0.003439942994905432</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.016572058274389734</v>
       </c>
       <c r="B18">
-        <v>0.0036802054125127967</v>
+        <v>0.003485055827547824</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.017546885231706773</v>
       </c>
       <c r="B19">
-        <v>0.0037056535329213795</v>
+        <v>0.0035115207412160392</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.018521712189023817</v>
       </c>
       <c r="B20">
-        <v>0.0037126643008534208</v>
+        <v>0.0035205162568080687</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.01949653914634086</v>
       </c>
       <c r="B21">
-        <v>0.0037026492695677515</v>
+        <v>0.0035132208952219045</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.020471366103657903</v>
       </c>
       <c r="B22">
-        <v>0.0036767668258047719</v>
+        <v>0.003490601477533876</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.021446193060974946</v>
       </c>
       <c r="B23">
-        <v>0.0036351626902311517</v>
+        <v>0.0034527780255336729</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.022421020018291993</v>
       </c>
       <c r="B24">
-        <v>0.0035777294169951289</v>
+        <v>0.0033996588611893215</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.023395846975609036</v>
       </c>
       <c r="B25">
-        <v>0.0035043595602449419</v>
+        <v>0.0033311523064688503</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.024370673932926076</v>
       </c>
       <c r="B26">
-        <v>0.0034149005256898304</v>
+        <v>0.0032471283465059721</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.025345500890243119</v>
       </c>
       <c r="B27">
-        <v>0.0033090191252830329</v>
+        <v>0.0031473036190971357</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.026320327847560162</v>
       </c>
       <c r="B28">
-        <v>0.0031863370225387903</v>
+        <v>0.0030313564252044769</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.027295154804877205</v>
       </c>
       <c r="B29">
-        <v>0.0030464758809713435</v>
+        <v>0.0028989650657901289</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.028269981762194252</v>
       </c>
       <c r="B30">
-        <v>0.0028892384533142166</v>
+        <v>0.0027499579924645987</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.029244808719511288</v>
       </c>
       <c r="B31">
-        <v>0.0027151518491780715</v>
+        <v>0.0025847642594318833</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.030219635676828335</v>
       </c>
       <c r="B32">
-        <v>0.0025249242673928518</v>
+        <v>0.002403963071544348</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.031194462634145378</v>
       </c>
       <c r="B33">
-        <v>0.0023192639067885043</v>
+        <v>0.0022081336336543613</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.032169289591462424</v>
       </c>
       <c r="B34">
-        <v>0.0020985742366709547</v>
+        <v>0.0019976003444159202</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.033144116548779468</v>
       </c>
       <c r="B35">
-        <v>0.0018620398082500576</v>
+        <v>0.0017716683776895427</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.034118943506096504</v>
       </c>
       <c r="B36">
-        <v>0.0016085404432116498</v>
+        <v>0.0015293881011373767</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.035093770463413547</v>
       </c>
       <c r="B37">
-        <v>0.0013369559632415648</v>
+        <v>0.0012698098824215668</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.03606859742073059</v>
       </c>
       <c r="B38">
-        <v>0.0010454261380293708</v>
+        <v>0.00099136651202981073</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.037043424378047633</v>
       </c>
       <c r="B39">
-        <v>0.00072913052927956173</v>
+        <v>0.000690020471752002</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.038018251335364683</v>
       </c>
       <c r="B40">
-        <v>0.00038250864670036241</v>
+        <v>0.00036111666620358359</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.03899307829268172</v>
       </c>
       <c r="B42">
-        <v>-3.3821104157458308E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.038018251335364683</v>
       </c>
       <c r="B43">
-        <v>0.00012580488073901612</v>
+        <v>0.00014719686123579497</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.037043424378047633</v>
       </c>
       <c r="B44">
-        <v>0.00025980983894884546</v>
+        <v>0.00029891989647640513</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.03606859742073059</v>
       </c>
       <c r="B45">
-        <v>0.00039671062603464935</v>
+        <v>0.00045077025203420944</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.035093770463413547</v>
       </c>
       <c r="B46">
-        <v>0.00053120299340158976</v>
+        <v>0.00059834907422158762</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.034118943506096504</v>
       </c>
       <c r="B47">
-        <v>0.00065871233832037279</v>
+        <v>0.00073786468039464587</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.033144116548779468</v>
       </c>
       <c r="B48">
-        <v>0.00077758264152388151</v>
+        <v>0.00086795407208439628</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.032169289591462424</v>
       </c>
       <c r="B49">
-        <v>0.0008868875296105446</v>
+        <v>0.00098786142186557875</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.031194462634145378</v>
       </c>
       <c r="B50">
-        <v>0.00098570062917878931</v>
+        <v>0.0010968309023129321</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.030219635676828335</v>
       </c>
       <c r="B51">
-        <v>0.0010733899172108029</v>
+        <v>0.0011943511130593069</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.029244808719511288</v>
       </c>
       <c r="B52">
-        <v>0.0011505007722238123</v>
+        <v>0.0012808883619700006</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.028269981762194252</v>
       </c>
       <c r="B53">
-        <v>0.0012178729231188039</v>
+        <v>0.0013571533839684216</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.027295154804877205</v>
       </c>
       <c r="B54">
-        <v>0.0012763460987967649</v>
+        <v>0.0014238569139779797</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.026320327847560162</v>
       </c>
       <c r="B55">
-        <v>0.0013265698545270222</v>
+        <v>0.0014815504518613358</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.025345500890243119</v>
       </c>
       <c r="B56">
-        <v>0.0013684330510522658</v>
+        <v>0.0015301485572381628</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.024370673932926076</v>
       </c>
       <c r="B57">
-        <v>0.001401634375483527</v>
+        <v>0.0015694065546673856</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.023395846975609036</v>
       </c>
       <c r="B58">
-        <v>0.0014258725149318364</v>
+        <v>0.0015990797687079285</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.022421020018291993</v>
       </c>
       <c r="B59">
-        <v>0.0014408827473254345</v>
+        <v>0.0016189533031312421</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.021446193060974946</v>
       </c>
       <c r="B60">
-        <v>0.0014465467138613994</v>
+        <v>0.0016289313785588784</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.020471366103657903</v>
       </c>
       <c r="B61">
-        <v>0.0014427826465540183</v>
+        <v>0.0016289479948249142</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.01949653914634086</v>
       </c>
       <c r="B62">
-        <v>0.0014295087774175788</v>
+        <v>0.0016189371517634262</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.018521712189023817</v>
       </c>
       <c r="B63">
-        <v>0.0014068877723091954</v>
+        <v>0.0015990358163545475</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.017546885231706773</v>
       </c>
       <c r="B64">
-        <v>0.0013760600324572931</v>
+        <v>0.0015701928241626335</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.016572058274389734</v>
       </c>
       <c r="B65">
-        <v>0.0013384103929331235</v>
+        <v>0.0015335599778980964</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.015597231317072689</v>
       </c>
       <c r="B66">
-        <v>0.0012953236888079379</v>
+        <v>0.0014902890802713463</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.014622404359755644</v>
       </c>
       <c r="B67">
-        <v>0.0012463752615313915</v>
+        <v>0.0014400234303361176</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.013647577402438603</v>
       </c>
       <c r="B68">
-        <v>0.0011839024780667526</v>
+        <v>0.0013763723125194294</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.012672750445121559</v>
       </c>
       <c r="B69">
-        <v>0.0011019584959376814</v>
+        <v>0.0012943739713192231</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.011697923487804518</v>
       </c>
       <c r="B70">
-        <v>0.001008697609395798</v>
+        <v>0.0012008165061438408</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.010723096530487473</v>
       </c>
       <c r="B71">
-        <v>0.00091301008058194337</v>
+        <v>0.0011031006437442151</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.00974826957317043</v>
       </c>
       <c r="B72">
-        <v>0.00081262890646588936</v>
+        <v>0.00099932776533124927</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0087734426158533867</v>
       </c>
       <c r="B73">
-        <v>0.00070379912841941948</v>
+        <v>0.00088635849036287125</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0077986156585363444</v>
       </c>
       <c r="B74">
-        <v>0.00058797123059343569</v>
+        <v>0.00076538973682513747</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0068237887012193013</v>
       </c>
       <c r="B75">
-        <v>0.00046792313075211223</v>
+        <v>0.00063872380727578583</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.005848961743902259</v>
       </c>
       <c r="B76">
-        <v>0.00034653703833359433</v>
+        <v>0.00050874824403115027</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.004874134786585215</v>
       </c>
       <c r="B77">
-        <v>0.00022647021909949906</v>
+        <v>0.00037766225533885153</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0038993078292681722</v>
       </c>
       <c r="B78">
-        <v>0.00010937587243135905</v>
+        <v>0.000246826473413062</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0029244808719511295</v>
       </c>
       <c r="B79">
-        <v>-1.8636291729323389E-06</v>
+        <v>0.00011862498275145408</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0019496539146340861</v>
       </c>
       <c r="B80">
-        <v>-0.00010212391376382551</v>
+        <v>-2.6915641174871896E-06</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00097482695731704306</v>
       </c>
       <c r="B81">
-        <v>-0.00017866372226900816</v>
+        <v>-0.00010652652742754702</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0010567027551749218</v>
       </c>
       <c r="B2">
-        <v>0.00090361640820228316</v>
+        <v>0.00082542040431933907</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0021134055103498436</v>
       </c>
       <c r="B3">
-        <v>0.0014031993837717869</v>
+        <v>0.0012954157027439447</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0031701082655247654</v>
       </c>
       <c r="B4">
-        <v>0.0018336638438821841</v>
+        <v>0.0017030553833425638</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0042268110206996872</v>
       </c>
       <c r="B5">
-        <v>0.0022137487462186691</v>
+        <v>0.0020647536577390051</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0052835137758746086</v>
       </c>
       <c r="B6">
-        <v>0.0025511623807374607</v>
+        <v>0.0023872717127010105</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0063402165310495308</v>
       </c>
       <c r="B7">
-        <v>0.0028503454861716492</v>
+        <v>0.0026745101477105423</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0073969192862244531</v>
       </c>
       <c r="B8">
-        <v>0.0031139490497823336</v>
+        <v>0.002928802810120429</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0084536220413993744</v>
       </c>
       <c r="B9">
-        <v>0.003346046753078734</v>
+        <v>0.0031537268516368985</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0095103247965742949</v>
       </c>
       <c r="B10">
-        <v>0.0035510238523785743</v>
+        <v>0.0033531313143228365</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.010567027551749217</v>
       </c>
       <c r="B11">
-        <v>0.0037330892089854793</v>
+        <v>0.003530709497314378</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.011623730306924139</v>
       </c>
       <c r="B12">
-        <v>0.0038945206720362676</v>
+        <v>0.0036884643865400541</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.012680433062099062</v>
       </c>
       <c r="B13">
-        <v>0.0040300484370146168</v>
+        <v>0.0038217934580247422</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.013737135817273982</v>
       </c>
       <c r="B14">
-        <v>0.0041365410049015085</v>
+        <v>0.0039279645376138483</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.014793838572448906</v>
       </c>
       <c r="B15">
-        <v>0.00422696775232027</v>
+        <v>0.0040183323603385336</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.015850541327623827</v>
       </c>
       <c r="B16">
-        <v>0.0043132239180677379</v>
+        <v>0.0041033112233329521</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.016907244082798749</v>
       </c>
       <c r="B17">
-        <v>0.0043868073139924366</v>
+        <v>0.0041754667629574516</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.017963946837973671</v>
       </c>
       <c r="B18">
-        <v>0.0044367226023558437</v>
+        <v>0.0042251823873916588</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.01902064959314859</v>
       </c>
       <c r="B19">
-        <v>0.0044623992740195585</v>
+        <v>0.0042519612528661129</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.020077352348323516</v>
       </c>
       <c r="B20">
-        <v>0.00446587302699521</v>
+        <v>0.004257586452624083</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.021134055103498434</v>
       </c>
       <c r="B21">
-        <v>0.0044491795592944286</v>
+        <v>0.0042438410799088382</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.022190757858673357</v>
       </c>
       <c r="B22">
-        <v>0.00441399011624242</v>
+        <v>0.0042121887247653323</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.023247460613848279</v>
       </c>
       <c r="B23">
-        <v>0.0043605181324186905</v>
+        <v>0.0041628149644452588</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.0243041633690232</v>
       </c>
       <c r="B24">
-        <v>0.0042886125897163233</v>
+        <v>0.0040955858730019959</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.025360866124198123</v>
       </c>
       <c r="B25">
-        <v>0.0041981224700284019</v>
+        <v>0.0040103675244889218</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.026417568879373042</v>
       </c>
       <c r="B26">
-        <v>0.0040888329245154674</v>
+        <v>0.003906969545938806</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.027474271634547964</v>
       </c>
       <c r="B27">
-        <v>0.0039602737814078953</v>
+        <v>0.0037849757763019827</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.028530974389722887</v>
       </c>
       <c r="B28">
-        <v>0.0038119110382035218</v>
+        <v>0.0036439136075081761</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.029587677144897812</v>
       </c>
       <c r="B29">
-        <v>0.00364321069240018</v>
+        <v>0.0034833104314871115</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.030644379900072734</v>
       </c>
       <c r="B30">
-        <v>0.0034539019793255448</v>
+        <v>0.0033029233408942761</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.031701082655247653</v>
       </c>
       <c r="B31">
-        <v>0.0032447670856266516</v>
+        <v>0.0031034282312882148</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.032757785410422575</v>
       </c>
       <c r="B32">
-        <v>0.0030168514357803706</v>
+        <v>0.0028857306989532321</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.0338144881655975</v>
       </c>
       <c r="B33">
-        <v>0.002771200454263577</v>
+        <v>0.0026507363401736357</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.03487119092077242</v>
       </c>
       <c r="B34">
-        <v>0.0025084208440463345</v>
+        <v>0.0023989661461168753</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.035927893675947342</v>
       </c>
       <c r="B35">
-        <v>0.00222736442207147</v>
+        <v>0.0021294026874829827</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.036984596431122257</v>
       </c>
       <c r="B36">
-        <v>0.0019264442837750024</v>
+        <v>0.0018406439298551327</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.03804129918629718</v>
       </c>
       <c r="B37">
-        <v>0.0016040735245929463</v>
+        <v>0.0015312878388164979</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.0390980019414721</v>
       </c>
       <c r="B38">
-        <v>0.0012575973307780515</v>
+        <v>0.0011989972322593539</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.040154704696647031</v>
       </c>
       <c r="B39">
-        <v>0.00088008925184999184</v>
+        <v>0.00083769433731237415</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.041211407451821953</v>
       </c>
       <c r="B40">
-        <v>0.00046355492814517245</v>
+        <v>0.00044036623341333107</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.041211407451821953</v>
       </c>
       <c r="B43">
-        <v>9.2535812435714523E-05</v>
+        <v>0.00011572450716755563</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.040154704696647031</v>
       </c>
       <c r="B44">
-        <v>0.0002017706192481074</v>
+        <v>0.00024416553378572517</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.0390980019414721</v>
       </c>
       <c r="B45">
-        <v>0.00031999575447888865</v>
+        <v>0.00037859585299758626</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.03804129918629718</v>
       </c>
       <c r="B46">
-        <v>0.00043950255216976871</v>
+        <v>0.00051228823794621727</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.036984596431122257</v>
       </c>
       <c r="B47">
-        <v>0.00055363862105708343</v>
+        <v>0.00063943897497695343</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.035927893675947342</v>
       </c>
       <c r="B48">
-        <v>0.0006599766686556706</v>
+        <v>0.00075793840324415811</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.03487119092077242</v>
       </c>
       <c r="B49">
-        <v>0.00075714567717499476</v>
+        <v>0.00086660037510445361</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.0338144881655975</v>
       </c>
       <c r="B50">
-        <v>0.0008437746288245193</v>
+        <v>0.00096423874291446049</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.032757785410422575</v>
       </c>
       <c r="B51">
-        <v>0.00091891964654616375</v>
+        <v>0.0010500403833733018</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.031701082655247653</v>
       </c>
       <c r="B52">
-        <v>0.00098334541621167152</v>
+        <v>0.0011246842705501076</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.030644379900072734</v>
       </c>
       <c r="B53">
-        <v>0.0010382437644252418</v>
+        <v>0.0011892224028565105</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.029587677144897812</v>
       </c>
       <c r="B54">
-        <v>0.0010848065177910741</v>
+        <v>0.001244706778704143</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.028530974389722887</v>
       </c>
       <c r="B55">
-        <v>0.0011239521470779881</v>
+        <v>0.0012919495777733341</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.027474271634547964</v>
       </c>
       <c r="B56">
-        <v>0.0011555056997132858</v>
+        <v>0.0013308037048191991</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.026417568879373042</v>
       </c>
       <c r="B57">
-        <v>0.0011790188672888894</v>
+        <v>0.0013608822458655507</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.025360866124198123</v>
       </c>
       <c r="B58">
-        <v>0.0011940433413967209</v>
+        <v>0.001381798286936201</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.0243041633690232</v>
       </c>
       <c r="B59">
-        <v>0.001200185122287081</v>
+        <v>0.0013932118390014086</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.023247460613848279</v>
       </c>
       <c r="B60">
-        <v>0.0011972674448437826</v>
+        <v>0.0013949706128172142</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.022190757858673357</v>
       </c>
       <c r="B61">
-        <v>0.0011851678526090172</v>
+        <v>0.0013869692440861049</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.021134055103498434</v>
       </c>
       <c r="B62">
-        <v>0.0011637638891249765</v>
+        <v>0.001369102368510567</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.020077352348323516</v>
       </c>
       <c r="B63">
-        <v>0.0011332878370571764</v>
+        <v>0.0013415744114283032</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.01902064959314859</v>
       </c>
       <c r="B64">
-        <v>0.0010953909355644336</v>
+        <v>0.0013058289567178787</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.017963946837973671</v>
       </c>
       <c r="B65">
-        <v>0.0010520791629288898</v>
+        <v>0.0012636193778930744</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.016907244082798749</v>
       </c>
       <c r="B66">
-        <v>0.0010053584974326867</v>
+        <v>0.001216699048467671</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.015850541327623827</v>
       </c>
       <c r="B67">
-        <v>0.00095462080231116812</v>
+        <v>0.0011645334970459536</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.014793838572448906</v>
       </c>
       <c r="B68">
-        <v>0.00088880148061248594</v>
+        <v>0.0010974368725942224</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.013737135817273982</v>
       </c>
       <c r="B69">
-        <v>0.000799317528298943</v>
+        <v>0.0010078939955866033</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.012680433062099062</v>
       </c>
       <c r="B70">
-        <v>0.00069796877317663934</v>
+        <v>0.00090622375216651294</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.011623730306924139</v>
       </c>
       <c r="B71">
-        <v>0.000597620104096863</v>
+        <v>0.00080367638959307581</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.010567027551749217</v>
       </c>
       <c r="B72">
-        <v>0.00049501382224786321</v>
+        <v>0.0006973935339189642</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0095103247965742949</v>
       </c>
       <c r="B73">
-        <v>0.00038474324348678076</v>
+        <v>0.00058263578154251784</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0084536220413993744</v>
       </c>
       <c r="B74">
-        <v>0.00026892833000936205</v>
+        <v>0.00046124823145119771</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0073969192862244531</v>
       </c>
       <c r="B75">
-        <v>0.0001516092151918588</v>
+        <v>0.00033675545485376338</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0063402165310495308</v>
       </c>
       <c r="B76">
-        <v>3.69800707939369E-05</v>
+        <v>0.00021281540925504377</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0052835137758746086</v>
       </c>
       <c r="B77">
-        <v>-7.1088307845743019E-05</v>
+        <v>9.280236019070724E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0042268110206996872</v>
       </c>
       <c r="B78">
-        <v>-0.00017017266945595395</v>
+        <v>-2.1177580976289986E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0031701082655247654</v>
       </c>
       <c r="B79">
-        <v>-0.00025607152475174132</v>
+        <v>-0.00012546306421212116</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0021134055103498436</v>
       </c>
       <c r="B80">
-        <v>-0.00032133951267368526</v>
+        <v>-0.00021355583164584324</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0010567027551749218</v>
       </c>
       <c r="B81">
-        <v>-0.00034751965392482419</v>
+        <v>-0.00026932365004188</v>
       </c>
     </row>
     <row r="82" spans="1:2">
